--- a/ProjectsGitHubRepositoryLinks-KunalMaheshwari(85010944).xlsx
+++ b/ProjectsGitHubRepositoryLinks-KunalMaheshwari(85010944).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0377cb67aaf17726/Documents/GitHub/Kunal-Testing-Assignments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="379" documentId="8_{2A57F4CE-79A1-4120-B35A-97F80FFB0D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9931E74F-A4FB-44BC-9922-C8BC5AC859E6}"/>
+  <xr:revisionPtr revIDLastSave="380" documentId="8_{2A57F4CE-79A1-4120-B35A-97F80FFB0D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51E6FCDD-DB58-4AD8-B059-7E422355ECFD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B493A82B-AB54-495A-8162-692038215013}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="172">
   <si>
     <t>Projects GitHub Repository Links</t>
   </si>
@@ -1050,7 +1050,7 @@
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <f>COUNTA(A6:A113)</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>4</v>
@@ -1841,9 +1841,7 @@
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="13" t="s">
-        <v>164</v>
-      </c>
+      <c r="A76" s="13"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
     </row>

--- a/ProjectsGitHubRepositoryLinks-KunalMaheshwari(85010944).xlsx
+++ b/ProjectsGitHubRepositoryLinks-KunalMaheshwari(85010944).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0377cb67aaf17726/Documents/GitHub/Kunal-Testing-Assignments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="380" documentId="8_{2A57F4CE-79A1-4120-B35A-97F80FFB0D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51E6FCDD-DB58-4AD8-B059-7E422355ECFD}"/>
+  <xr:revisionPtr revIDLastSave="384" documentId="8_{2A57F4CE-79A1-4120-B35A-97F80FFB0D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{082B6117-02E0-472B-913F-C562143B6671}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B493A82B-AB54-495A-8162-692038215013}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -552,7 +551,7 @@
     <t>https://github.com/kunalwebdev1/Kunal-Testing-Assignments/tree/main/CoforgeSeleniumTesting/RESTAssuredWithBDDFramework</t>
   </si>
   <si>
-    <t>Altoro Mutual Testing</t>
+    <t>Hybrid Driven Framework-Altoro Mutual Testing</t>
   </si>
 </sst>
 </file>
@@ -630,7 +629,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -668,6 +667,12 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1030,11 +1035,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1841,39 +1846,39 @@
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="13"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
+      <c r="A76" s="17"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="18"/>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="15"/>
-      <c r="B77" s="16"/>
-      <c r="C77" s="16"/>
+      <c r="A77" s="14"/>
+      <c r="B77" s="15"/>
+      <c r="C77" s="15"/>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="15"/>
-      <c r="B78" s="16"/>
-      <c r="C78" s="16"/>
+      <c r="A78" s="14"/>
+      <c r="B78" s="15"/>
+      <c r="C78" s="15"/>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="15"/>
-      <c r="B79" s="16"/>
-      <c r="C79" s="16"/>
+      <c r="A79" s="14"/>
+      <c r="B79" s="15"/>
+      <c r="C79" s="15"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="15"/>
-      <c r="B80" s="16"/>
-      <c r="C80" s="16"/>
+      <c r="A80" s="14"/>
+      <c r="B80" s="15"/>
+      <c r="C80" s="15"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="15"/>
-      <c r="B81" s="16"/>
-      <c r="C81" s="16"/>
+      <c r="A81" s="14"/>
+      <c r="B81" s="15"/>
+      <c r="C81" s="15"/>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="15"/>
-      <c r="B82" s="16"/>
-      <c r="C82" s="16"/>
+      <c r="A82" s="14"/>
+      <c r="B82" s="15"/>
+      <c r="C82" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ProjectsGitHubRepositoryLinks-KunalMaheshwari(85010944).xlsx
+++ b/ProjectsGitHubRepositoryLinks-KunalMaheshwari(85010944).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0377cb67aaf17726/Documents/GitHub/Kunal-Testing-Assignments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="384" documentId="8_{2A57F4CE-79A1-4120-B35A-97F80FFB0D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{082B6117-02E0-472B-913F-C562143B6671}"/>
+  <xr:revisionPtr revIDLastSave="388" documentId="8_{2A57F4CE-79A1-4120-B35A-97F80FFB0D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07D62BD3-5F38-4506-A48F-620C98BC1EA1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B493A82B-AB54-495A-8162-692038215013}"/>
   </bookViews>
@@ -545,13 +545,13 @@
     <t>https://github.com/kunalwebdev1/Kunal-Testing-Assignments/tree/main/JMeterFiles/NON%20GUI%20Mode</t>
   </si>
   <si>
-    <t>https://github.com/kunalwebdev1/Kunal-Testing-Assignments/tree/main/CoforgeSeleniumTesting/AltoroMutualTesting</t>
-  </si>
-  <si>
     <t>https://github.com/kunalwebdev1/Kunal-Testing-Assignments/tree/main/CoforgeSeleniumTesting/RESTAssuredWithBDDFramework</t>
   </si>
   <si>
     <t>Hybrid Driven Framework-Altoro Mutual Testing</t>
+  </si>
+  <si>
+    <t>https://github.com/kunalwebdev1/Kunal-Testing-Assignments/tree/main/Hybrid%20Driven%20Framework/AltoroMutualTesting</t>
   </si>
 </sst>
 </file>
@@ -1030,7 +1030,7 @@
   <cols>
     <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39.85546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="52.28515625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="53.7109375" style="3" customWidth="1"/>
     <col min="4" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
@@ -1831,7 +1831,7 @@
         <v>162</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -1839,10 +1839,10 @@
         <v>164</v>
       </c>
       <c r="B75" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C75" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -1959,6 +1959,6 @@
     <hyperlink ref="C74" r:id="rId71" xr:uid="{0E61B184-57F8-4CF3-8D23-B42EF6747AC3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="84" fitToHeight="0" orientation="portrait" r:id="rId72"/>
+  <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="portrait" r:id="rId72"/>
 </worksheet>
 </file>